--- a/lexicon/lexicon.xlsx
+++ b/lexicon/lexicon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\Github\upta\khallam\lexicon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E772B7-8EE2-4270-B62F-3363D817E461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E009B29-C591-4556-BEA8-C9725B6F026F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10695" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lexicon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="406">
   <si>
     <t>id (filled in for you)</t>
   </si>
@@ -995,13 +995,256 @@
   </si>
   <si>
     <t>sáy̓siʔ</t>
+  </si>
+  <si>
+    <t>kʷánəŋət</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>ch-1.1</t>
+  </si>
+  <si>
+    <t>nə́qəŋ</t>
+  </si>
+  <si>
+    <t>dive</t>
+  </si>
+  <si>
+    <t>kʷə́yəŋ</t>
+  </si>
+  <si>
+    <t>fly</t>
+  </si>
+  <si>
+    <t>ɬáw̓</t>
+  </si>
+  <si>
+    <t>run away</t>
+  </si>
+  <si>
+    <t>xʷítəŋ</t>
+  </si>
+  <si>
+    <t>jump</t>
+  </si>
+  <si>
+    <t>šə́wi</t>
+  </si>
+  <si>
+    <t>grow</t>
+  </si>
+  <si>
+    <t>ʔíc̓əŋ</t>
+  </si>
+  <si>
+    <t>get dressed</t>
+  </si>
+  <si>
+    <t>kʷənáŋət</t>
+  </si>
+  <si>
+    <t>help it/him/her/them</t>
+  </si>
+  <si>
+    <t>ch-1.2</t>
+  </si>
+  <si>
+    <t>k̓ʷə́nt</t>
+  </si>
+  <si>
+    <t>look at it</t>
+  </si>
+  <si>
+    <t>c̓čə́t</t>
+  </si>
+  <si>
+    <t>wake it</t>
+  </si>
+  <si>
+    <t>x̣áčt</t>
+  </si>
+  <si>
+    <t>dry it</t>
+  </si>
+  <si>
+    <t>ƛ̓kʷít</t>
+  </si>
+  <si>
+    <t>hold it</t>
+  </si>
+  <si>
+    <t>šč̓ə́t</t>
+  </si>
+  <si>
+    <t>hit it</t>
+  </si>
+  <si>
+    <t>sáʔət</t>
+  </si>
+  <si>
+    <t>lift it</t>
+  </si>
+  <si>
+    <t>míst</t>
+  </si>
+  <si>
+    <t>choose it</t>
+  </si>
+  <si>
+    <t>tkʷə́t</t>
+  </si>
+  <si>
+    <t>break it (long object)</t>
+  </si>
+  <si>
+    <t>ƛ̓kʷə́t</t>
+  </si>
+  <si>
+    <t>take it</t>
+  </si>
+  <si>
+    <t>cə́t</t>
+  </si>
+  <si>
+    <t>father</t>
+  </si>
+  <si>
+    <t>ch-4</t>
+  </si>
+  <si>
+    <t>tálə</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>swéʔwəs</t>
+  </si>
+  <si>
+    <t>young man</t>
+  </si>
+  <si>
+    <t>sčáʔčaʔ</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>sqʷáy</t>
+  </si>
+  <si>
+    <t>word</t>
+  </si>
+  <si>
+    <t>ʔəsx̣áʔəs</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>ch-6</t>
+  </si>
+  <si>
+    <t>kʷɬčə́q</t>
+  </si>
+  <si>
+    <t>old (animate)</t>
+  </si>
+  <si>
+    <t>ʔəsc̓áx̣ɬ</t>
+  </si>
+  <si>
+    <t>old / worn out (thing)</t>
+  </si>
+  <si>
+    <t>small / few</t>
+  </si>
+  <si>
+    <t>much / many</t>
+  </si>
+  <si>
+    <t>x̣ʷə́ŋ</t>
+  </si>
+  <si>
+    <t>fast</t>
+  </si>
+  <si>
+    <t>cn</t>
+  </si>
+  <si>
+    <t>I (intransitive)</t>
+  </si>
+  <si>
+    <t>st</t>
+  </si>
+  <si>
+    <t>we (intransitive)</t>
+  </si>
+  <si>
+    <t>cxʷ</t>
+  </si>
+  <si>
+    <t>you (intransitive)</t>
+  </si>
+  <si>
+    <t>cxʷ hay</t>
+  </si>
+  <si>
+    <t>you all / you folks (intransitive)</t>
+  </si>
+  <si>
+    <t>-s</t>
+  </si>
+  <si>
+    <t>he / she / it / they (transitive suffix)</t>
+  </si>
+  <si>
+    <t>cə</t>
+  </si>
+  <si>
+    <t>the / that (specific article)</t>
+  </si>
+  <si>
+    <t>nəxʷ</t>
+  </si>
+  <si>
+    <t>your</t>
+  </si>
+  <si>
+    <t>čáy</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>ƛ̓áɬəŋ</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>sk̓ʷtúʔ</t>
+  </si>
+  <si>
+    <t>raven</t>
+  </si>
+  <si>
+    <t>séʔyaʔ</t>
+  </si>
+  <si>
+    <t>grandparent</t>
+  </si>
+  <si>
+    <t>pronouns</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1014,8 +1257,21 @@
     <font>
       <i/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1044,13 +1300,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1385,8 +1645,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E139"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" style="3" customWidth="1"/>
     <col min="2" max="2" width="22" style="2" customWidth="1"/>
@@ -1395,7 +1655,7 @@
     <col min="5" max="5" width="24" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,7 +1672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1426,7 +1686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1440,7 +1700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1454,7 +1714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1467,8 +1727,11 @@
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -1482,7 +1745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1495,8 +1758,11 @@
       <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -1510,7 +1776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -1524,7 +1790,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
@@ -1538,7 +1804,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
@@ -1551,8 +1817,11 @@
       <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
@@ -1565,8 +1834,11 @@
       <c r="D12" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
@@ -1580,7 +1852,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
@@ -1594,7 +1866,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -1608,7 +1880,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
@@ -1622,7 +1894,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>51</v>
       </c>
@@ -1636,7 +1908,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>54</v>
       </c>
@@ -1650,7 +1922,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -1664,7 +1936,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>60</v>
       </c>
@@ -1677,8 +1949,11 @@
       <c r="D20" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -1691,8 +1966,11 @@
       <c r="D21" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>66</v>
       </c>
@@ -1706,7 +1984,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>69</v>
       </c>
@@ -1719,8 +1997,11 @@
       <c r="D23" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>72</v>
       </c>
@@ -1734,7 +2015,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>75</v>
       </c>
@@ -1748,7 +2029,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>78</v>
       </c>
@@ -1761,8 +2042,11 @@
       <c r="D26" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>81</v>
       </c>
@@ -1776,7 +2060,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>84</v>
       </c>
@@ -1790,7 +2074,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>87</v>
       </c>
@@ -1804,7 +2088,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>90</v>
       </c>
@@ -1818,7 +2102,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>94</v>
       </c>
@@ -1832,7 +2116,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>97</v>
       </c>
@@ -1846,7 +2130,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>100</v>
       </c>
@@ -1860,7 +2144,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
@@ -1874,7 +2158,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>106</v>
       </c>
@@ -1888,7 +2172,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>109</v>
       </c>
@@ -1902,7 +2186,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>112</v>
       </c>
@@ -1916,7 +2200,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>115</v>
       </c>
@@ -1930,7 +2214,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>118</v>
       </c>
@@ -1943,8 +2227,11 @@
       <c r="D39" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>121</v>
       </c>
@@ -1958,7 +2245,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>125</v>
       </c>
@@ -1972,7 +2259,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>129</v>
       </c>
@@ -1985,8 +2272,11 @@
       <c r="D42" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>132</v>
       </c>
@@ -2000,7 +2290,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>135</v>
       </c>
@@ -2014,7 +2304,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>138</v>
       </c>
@@ -2028,7 +2318,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>141</v>
       </c>
@@ -2042,7 +2332,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>144</v>
       </c>
@@ -2055,8 +2345,11 @@
       <c r="D47" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>147</v>
       </c>
@@ -2070,7 +2363,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>151</v>
       </c>
@@ -2084,7 +2377,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>154</v>
       </c>
@@ -2098,7 +2391,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>158</v>
       </c>
@@ -2112,7 +2405,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>161</v>
       </c>
@@ -2126,7 +2419,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>164</v>
       </c>
@@ -2139,8 +2432,11 @@
       <c r="D53" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>168</v>
       </c>
@@ -2154,7 +2450,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>171</v>
       </c>
@@ -2168,7 +2464,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>174</v>
       </c>
@@ -2182,7 +2478,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>177</v>
       </c>
@@ -2196,7 +2492,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>180</v>
       </c>
@@ -2209,8 +2505,11 @@
       <c r="D58" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>183</v>
       </c>
@@ -2224,7 +2523,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>186</v>
       </c>
@@ -2232,13 +2531,16 @@
         <v>187</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>186</v>
+        <v>380</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>189</v>
       </c>
@@ -2252,7 +2554,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>193</v>
       </c>
@@ -2265,8 +2567,11 @@
       <c r="D62" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>196</v>
       </c>
@@ -2280,7 +2585,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>199</v>
       </c>
@@ -2294,7 +2599,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>202</v>
       </c>
@@ -2308,7 +2613,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>205</v>
       </c>
@@ -2322,7 +2627,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>208</v>
       </c>
@@ -2336,7 +2641,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>211</v>
       </c>
@@ -2350,7 +2655,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>214</v>
       </c>
@@ -2363,8 +2668,11 @@
       <c r="D69" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>218</v>
       </c>
@@ -2375,7 +2683,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>220</v>
       </c>
@@ -2389,7 +2697,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>223</v>
       </c>
@@ -2403,7 +2711,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>226</v>
       </c>
@@ -2417,7 +2725,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>230</v>
       </c>
@@ -2431,7 +2739,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>233</v>
       </c>
@@ -2445,7 +2753,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>237</v>
       </c>
@@ -2458,8 +2766,11 @@
       <c r="D76" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>240</v>
       </c>
@@ -2467,13 +2778,16 @@
         <v>241</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>240</v>
+        <v>379</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>243</v>
       </c>
@@ -2487,7 +2801,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>246</v>
       </c>
@@ -2500,8 +2814,11 @@
       <c r="D79" s="2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>249</v>
       </c>
@@ -2514,8 +2831,11 @@
       <c r="D80" s="2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>252</v>
       </c>
@@ -2529,7 +2849,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>255</v>
       </c>
@@ -2543,7 +2863,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>258</v>
       </c>
@@ -2557,7 +2877,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>261</v>
       </c>
@@ -2571,7 +2891,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>264</v>
       </c>
@@ -2585,7 +2905,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>267</v>
       </c>
@@ -2599,7 +2919,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>270</v>
       </c>
@@ -2610,7 +2930,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>272</v>
       </c>
@@ -2623,8 +2943,11 @@
       <c r="D88" s="2" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>276</v>
       </c>
@@ -2637,8 +2960,11 @@
       <c r="D89" s="2" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>279</v>
       </c>
@@ -2651,8 +2977,11 @@
       <c r="D90" s="2" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>282</v>
       </c>
@@ -2666,7 +2995,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>286</v>
       </c>
@@ -2680,7 +3009,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>289</v>
       </c>
@@ -2693,8 +3022,11 @@
       <c r="D93" s="2" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>292</v>
       </c>
@@ -2708,7 +3040,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>296</v>
       </c>
@@ -2722,7 +3054,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>300</v>
       </c>
@@ -2736,7 +3068,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>303</v>
       </c>
@@ -2747,7 +3079,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>305</v>
       </c>
@@ -2761,7 +3093,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>308</v>
       </c>
@@ -2774,8 +3106,11 @@
       <c r="D99" s="2" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>312</v>
       </c>
@@ -2789,7 +3124,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>314</v>
       </c>
@@ -2803,8 +3138,8 @@
         <v>317</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="4" t="s">
         <v>319</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -2815,10 +3150,588 @@
       </c>
       <c r="D102" s="2" t="s">
         <v>320</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dive</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fly</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">run-away</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jump</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grow</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">get-dressed</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">help-it-him-her-them</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">look-at-it</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wake-it</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dry-it</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hold-it</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-it</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lift-it</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">choose-it</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">break-it-long-object</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">take-it</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">father</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">money</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">young-man</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friend</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">word</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old-animate</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old-worn-out-thing</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fast</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i-intransitive</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">we-intransitive</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">you-intransitive</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">you-all-you-folks-intransitive</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">he-she-it-they-transitive-suffix</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the-that-specific-article</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">your</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">work</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salt</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raven</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grandparent</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/lexicon/lexicon.xlsx
+++ b/lexicon/lexicon.xlsx
@@ -1673,8 +1673,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">afraid</t>
+        </is>
       </c>
       <c r="B2" s="2" t="s">
         <v>324</v>
@@ -1687,8 +1689,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -1701,8 +1705,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basket</t>
+        </is>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -1715,8 +1721,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">big</t>
+        </is>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
@@ -1732,8 +1740,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bird</t>
+        </is>
       </c>
       <c r="B6" s="2" t="s">
         <v>322</v>
@@ -1746,8 +1756,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">black</t>
+        </is>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
@@ -1763,8 +1775,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blackberry</t>
+        </is>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
@@ -1777,8 +1791,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>24</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bone-game</t>
+        </is>
       </c>
       <c r="B9" s="2" t="s">
         <v>25</v>
@@ -1791,8 +1807,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>28</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bread</t>
+        </is>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
@@ -1805,8 +1823,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">canoe</t>
+        </is>
       </c>
       <c r="B11" s="2" t="s">
         <v>32</v>
@@ -1822,8 +1842,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>34</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cat</t>
+        </is>
       </c>
       <c r="B12" s="2" t="s">
         <v>35</v>
@@ -1839,8 +1861,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cedar-wood</t>
+        </is>
       </c>
       <c r="B13" s="2" t="s">
         <v>38</v>
@@ -1853,8 +1877,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>41</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chinook-salmon</t>
+        </is>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
@@ -1867,8 +1893,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>45</v>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coat</t>
+        </is>
       </c>
       <c r="B15" s="2" t="s">
         <v>46</v>
@@ -1881,8 +1909,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>48</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">comb</t>
+        </is>
       </c>
       <c r="B16" s="2" t="s">
         <v>49</v>
@@ -1895,8 +1925,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>51</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continue</t>
+        </is>
       </c>
       <c r="B17" s="2" t="s">
         <v>52</v>
@@ -1909,8 +1941,10 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>54</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cow</t>
+        </is>
       </c>
       <c r="B18" s="2" t="s">
         <v>55</v>
@@ -1923,8 +1957,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>57</v>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crab</t>
+        </is>
       </c>
       <c r="B19" s="2" t="s">
         <v>58</v>
@@ -1937,8 +1973,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>60</v>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cry</t>
+        </is>
       </c>
       <c r="B20" s="2" t="s">
         <v>61</v>
@@ -1954,8 +1992,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>63</v>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cut-it</t>
+        </is>
       </c>
       <c r="B21" s="2" t="s">
         <v>323</v>
@@ -1971,8 +2011,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>66</v>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">day</t>
+        </is>
       </c>
       <c r="B22" s="2" t="s">
         <v>67</v>
@@ -1985,8 +2027,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>69</v>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deer</t>
+        </is>
       </c>
       <c r="B23" s="2" t="s">
         <v>70</v>
@@ -2002,8 +2046,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>72</v>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dirt</t>
+        </is>
       </c>
       <c r="B24" s="2" t="s">
         <v>73</v>
@@ -2016,8 +2062,10 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>75</v>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">disappear</t>
+        </is>
       </c>
       <c r="B25" s="2" t="s">
         <v>76</v>
@@ -2030,8 +2078,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>78</v>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dog</t>
+        </is>
       </c>
       <c r="B26" s="2" t="s">
         <v>79</v>
@@ -2047,8 +2097,10 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>81</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duck</t>
+        </is>
       </c>
       <c r="B27" s="2" t="s">
         <v>82</v>
@@ -2061,8 +2113,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>84</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ear</t>
+        </is>
       </c>
       <c r="B28" s="2" t="s">
         <v>85</v>
@@ -2075,8 +2129,10 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>87</v>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eat</t>
+        </is>
       </c>
       <c r="B29" s="2" t="s">
         <v>88</v>
@@ -2089,8 +2145,10 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>90</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">elwha</t>
+        </is>
       </c>
       <c r="B30" s="2" t="s">
         <v>91</v>
@@ -2103,8 +2161,10 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>94</v>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enter</t>
+        </is>
       </c>
       <c r="B31" s="2" t="s">
         <v>95</v>
@@ -2117,8 +2177,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>97</v>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evening</t>
+        </is>
       </c>
       <c r="B32" s="2" t="s">
         <v>98</v>
@@ -2131,8 +2193,10 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>100</v>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">finish</t>
+        </is>
       </c>
       <c r="B33" s="2" t="s">
         <v>101</v>
@@ -2145,8 +2209,10 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>103</v>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">five</t>
+        </is>
       </c>
       <c r="B34" s="2" t="s">
         <v>104</v>
@@ -2159,8 +2225,10 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>106</v>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flip</t>
+        </is>
       </c>
       <c r="B35" s="2" t="s">
         <v>107</v>
@@ -2173,8 +2241,10 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>109</v>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flounder</t>
+        </is>
       </c>
       <c r="B36" s="2" t="s">
         <v>110</v>
@@ -2187,8 +2257,10 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>112</v>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foot</t>
+        </is>
       </c>
       <c r="B37" s="2" t="s">
         <v>113</v>
@@ -2201,8 +2273,10 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>115</v>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">four</t>
+        </is>
       </c>
       <c r="B38" s="2" t="s">
         <v>116</v>
@@ -2215,8 +2289,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>118</v>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">go</t>
+        </is>
       </c>
       <c r="B39" s="2" t="s">
         <v>119</v>
@@ -2232,8 +2308,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>121</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">go-home</t>
+        </is>
       </c>
       <c r="B40" s="2" t="s">
         <v>122</v>
@@ -2246,8 +2324,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>125</v>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">go-with</t>
+        </is>
       </c>
       <c r="B41" s="2" t="s">
         <v>126</v>
@@ -2260,8 +2340,10 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>129</v>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">good</t>
+        </is>
       </c>
       <c r="B42" s="2" t="s">
         <v>130</v>
@@ -2277,8 +2359,10 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>132</v>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodbye</t>
+        </is>
       </c>
       <c r="B43" s="2" t="s">
         <v>133</v>
@@ -2291,8 +2375,10 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>135</v>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hand</t>
+        </is>
       </c>
       <c r="B44" s="2" t="s">
         <v>136</v>
@@ -2305,8 +2391,10 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>138</v>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hat</t>
+        </is>
       </c>
       <c r="B45" s="2" t="s">
         <v>139</v>
@@ -2319,8 +2407,10 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>141</v>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart</t>
+        </is>
       </c>
       <c r="B46" s="2" t="s">
         <v>142</v>
@@ -2333,8 +2423,10 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>144</v>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house</t>
+        </is>
       </c>
       <c r="B47" s="2" t="s">
         <v>145</v>
@@ -2350,8 +2442,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>147</v>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how-many</t>
+        </is>
       </c>
       <c r="B48" s="2" t="s">
         <v>148</v>
@@ -2364,8 +2458,10 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>151</v>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hungry</t>
+        </is>
       </c>
       <c r="B49" s="2" t="s">
         <v>152</v>
@@ -2378,8 +2474,10 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>154</v>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">important-person</t>
+        </is>
       </c>
       <c r="B50" s="2" t="s">
         <v>155</v>
@@ -2392,8 +2490,10 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>158</v>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jellyfish</t>
+        </is>
       </c>
       <c r="B51" s="2" t="s">
         <v>159</v>
@@ -2406,8 +2506,10 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>161</v>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
       </c>
       <c r="B52" s="2" t="s">
         <v>162</v>
@@ -2420,8 +2522,10 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>164</v>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">know-it</t>
+        </is>
       </c>
       <c r="B53" s="2" t="s">
         <v>165</v>
@@ -2437,8 +2541,10 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>168</v>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laugh</t>
+        </is>
       </c>
       <c r="B54" s="2" t="s">
         <v>169</v>
@@ -2451,8 +2557,10 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>171</v>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">like</t>
+        </is>
       </c>
       <c r="B55" s="2" t="s">
         <v>172</v>
@@ -2465,8 +2573,10 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>174</v>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">long</t>
+        </is>
       </c>
       <c r="B56" s="2" t="s">
         <v>175</v>
@@ -2479,8 +2589,10 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>177</v>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">man</t>
+        </is>
       </c>
       <c r="B57" s="2" t="s">
         <v>178</v>
@@ -2493,8 +2605,10 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
-        <v>180</v>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mother</t>
+        </is>
       </c>
       <c r="B58" s="2" t="s">
         <v>181</v>
@@ -2510,8 +2624,10 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>183</v>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouth</t>
+        </is>
       </c>
       <c r="B59" s="2" t="s">
         <v>184</v>
@@ -2524,8 +2640,10 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
-        <v>186</v>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">much</t>
+        </is>
       </c>
       <c r="B60" s="2" t="s">
         <v>187</v>
@@ -2541,8 +2659,10 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>189</v>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">my-child</t>
+        </is>
       </c>
       <c r="B61" s="2" t="s">
         <v>190</v>
@@ -2555,8 +2675,10 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>193</v>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new</t>
+        </is>
       </c>
       <c r="B62" s="2" t="s">
         <v>194</v>
@@ -2572,8 +2694,10 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
-        <v>196</v>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one</t>
+        </is>
       </c>
       <c r="B63" s="2" t="s">
         <v>197</v>
@@ -2586,8 +2710,10 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>199</v>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">outside</t>
+        </is>
       </c>
       <c r="B64" s="2" t="s">
         <v>200</v>
@@ -2600,8 +2726,10 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>202</v>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">play</t>
+        </is>
       </c>
       <c r="B65" s="2" t="s">
         <v>203</v>
@@ -2614,8 +2742,10 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>205</v>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">potato</t>
+        </is>
       </c>
       <c r="B66" s="2" t="s">
         <v>206</v>
@@ -2628,8 +2758,10 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>208</v>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raccoon</t>
+        </is>
       </c>
       <c r="B67" s="2" t="s">
         <v>209</v>
@@ -2642,8 +2774,10 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>211</v>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rat</t>
+        </is>
       </c>
       <c r="B68" s="2" t="s">
         <v>212</v>
@@ -2656,8 +2790,10 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>214</v>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">road-door</t>
+        </is>
       </c>
       <c r="B69" s="2" t="s">
         <v>215</v>
@@ -2673,8 +2809,10 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>218</v>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sack</t>
+        </is>
       </c>
       <c r="B70" s="2" t="s">
         <v>219</v>
@@ -2684,8 +2822,10 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>220</v>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scratch</t>
+        </is>
       </c>
       <c r="B71" s="2" t="s">
         <v>221</v>
@@ -2698,8 +2838,10 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>223</v>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sheep</t>
+        </is>
       </c>
       <c r="B72" s="2" t="s">
         <v>224</v>
@@ -2712,8 +2854,10 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>226</v>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sit-down</t>
+        </is>
       </c>
       <c r="B73" s="2" t="s">
         <v>227</v>
@@ -2726,8 +2870,10 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>230</v>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">six</t>
+        </is>
       </c>
       <c r="B74" s="2" t="s">
         <v>231</v>
@@ -2740,8 +2886,10 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>233</v>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skin-hide</t>
+        </is>
       </c>
       <c r="B75" s="2" t="s">
         <v>234</v>
@@ -2754,8 +2902,10 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>237</v>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sleep</t>
+        </is>
       </c>
       <c r="B76" s="2" t="s">
         <v>238</v>
@@ -2771,8 +2921,10 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>240</v>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">small</t>
+        </is>
       </c>
       <c r="B77" s="2" t="s">
         <v>241</v>
@@ -2788,8 +2940,10 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>243</v>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sneezing</t>
+        </is>
       </c>
       <c r="B78" s="2" t="s">
         <v>244</v>
@@ -2802,8 +2956,10 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
-        <v>246</v>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stick</t>
+        </is>
       </c>
       <c r="B79" s="2" t="s">
         <v>247</v>
@@ -2819,8 +2975,10 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>249</v>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strong</t>
+        </is>
       </c>
       <c r="B80" s="2" t="s">
         <v>250</v>
@@ -2836,8 +2994,10 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>252</v>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">talking</t>
+        </is>
       </c>
       <c r="B81" s="2" t="s">
         <v>253</v>
@@ -2850,8 +3010,10 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
-        <v>255</v>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ten</t>
+        </is>
       </c>
       <c r="B82" s="2" t="s">
         <v>256</v>
@@ -2864,8 +3026,10 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
-        <v>258</v>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">three</t>
+        </is>
       </c>
       <c r="B83" s="2" t="s">
         <v>259</v>
@@ -2878,8 +3042,10 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>261</v>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tide</t>
+        </is>
       </c>
       <c r="B84" s="2" t="s">
         <v>262</v>
@@ -2892,8 +3058,10 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
-        <v>264</v>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongue</t>
+        </is>
       </c>
       <c r="B85" s="2" t="s">
         <v>265</v>
@@ -2906,8 +3074,10 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
-        <v>267</v>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tooth</t>
+        </is>
       </c>
       <c r="B86" s="2" t="s">
         <v>268</v>
@@ -2920,8 +3090,10 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
-        <v>270</v>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trying-it</t>
+        </is>
       </c>
       <c r="B87" s="2" t="s">
         <v>321</v>
@@ -2931,8 +3103,10 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
-        <v>272</v>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uncle-aunt</t>
+        </is>
       </c>
       <c r="B88" s="2" t="s">
         <v>273</v>
@@ -2948,8 +3122,10 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
-        <v>276</v>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">walk</t>
+        </is>
       </c>
       <c r="B89" s="2" t="s">
         <v>277</v>
@@ -2965,8 +3141,10 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>279</v>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">water</t>
+        </is>
       </c>
       <c r="B90" s="2" t="s">
         <v>280</v>
@@ -2982,8 +3160,10 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
-        <v>282</v>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what</t>
+        </is>
       </c>
       <c r="B91" s="2" t="s">
         <v>283</v>
@@ -2996,8 +3176,10 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>286</v>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whistle</t>
+        </is>
       </c>
       <c r="B92" s="2" t="s">
         <v>287</v>
@@ -3010,8 +3192,10 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
-        <v>289</v>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">white</t>
+        </is>
       </c>
       <c r="B93" s="2" t="s">
         <v>290</v>
@@ -3027,8 +3211,10 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="3" t="s">
-        <v>292</v>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">white-person</t>
+        </is>
       </c>
       <c r="B94" s="2" t="s">
         <v>293</v>
@@ -3041,8 +3227,10 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
-        <v>296</v>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">who</t>
+        </is>
       </c>
       <c r="B95" s="2" t="s">
         <v>297</v>
@@ -3055,8 +3243,10 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
-        <v>300</v>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wishing</t>
+        </is>
       </c>
       <c r="B96" s="2" t="s">
         <v>301</v>
@@ -3069,8 +3259,10 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="3" t="s">
-        <v>303</v>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
       </c>
       <c r="B97" s="2" t="s">
         <v>304</v>
@@ -3080,8 +3272,10 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="3" t="s">
-        <v>305</v>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">you</t>
+        </is>
       </c>
       <c r="B98" s="2" t="s">
         <v>306</v>
@@ -3094,8 +3288,10 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
-        <v>308</v>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">young-woman</t>
+        </is>
       </c>
       <c r="B99" s="2" t="s">
         <v>309</v>
@@ -3111,8 +3307,10 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="3" t="s">
-        <v>312</v>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">young-woman-2</t>
+        </is>
       </c>
       <c r="B100" s="2" t="s">
         <v>313</v>
@@ -3125,8 +3323,10 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
-        <v>314</v>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">your-mother</t>
+        </is>
       </c>
       <c r="B101" s="2" t="s">
         <v>315</v>
@@ -3139,8 +3339,10 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" s="4" t="s">
-        <v>319</v>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">two</t>
+        </is>
       </c>
       <c r="B102" s="2" t="s">
         <v>318</v>
@@ -3153,7 +3355,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run</t>
         </is>
@@ -3169,7 +3371,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">dive</t>
         </is>
@@ -3185,7 +3387,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">fly</t>
         </is>
@@ -3201,7 +3403,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">run-away</t>
         </is>
@@ -3217,7 +3419,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">jump</t>
         </is>
@@ -3233,7 +3435,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">grow</t>
         </is>
@@ -3249,7 +3451,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">get-dressed</t>
         </is>
@@ -3265,7 +3467,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">help-it-him-her-them</t>
         </is>
@@ -3281,7 +3483,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">look-at-it</t>
         </is>
@@ -3297,7 +3499,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">wake-it</t>
         </is>
@@ -3313,7 +3515,7 @@
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">dry-it</t>
         </is>
@@ -3329,7 +3531,7 @@
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">hold-it</t>
         </is>
@@ -3345,7 +3547,7 @@
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">hit-it</t>
         </is>
@@ -3361,7 +3563,7 @@
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">lift-it</t>
         </is>
@@ -3377,7 +3579,7 @@
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">choose-it</t>
         </is>
@@ -3393,7 +3595,7 @@
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">break-it-long-object</t>
         </is>
@@ -3409,7 +3611,7 @@
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">take-it</t>
         </is>
@@ -3425,7 +3627,7 @@
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">father</t>
         </is>
@@ -3441,7 +3643,7 @@
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">money</t>
         </is>
@@ -3457,7 +3659,7 @@
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">young-man</t>
         </is>
@@ -3473,7 +3675,7 @@
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">friend</t>
         </is>
@@ -3489,7 +3691,7 @@
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">word</t>
         </is>
@@ -3505,7 +3707,7 @@
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">bad</t>
         </is>
@@ -3521,7 +3723,7 @@
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">old-animate</t>
         </is>
@@ -3537,7 +3739,7 @@
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">old-worn-out-thing</t>
         </is>
@@ -3553,7 +3755,7 @@
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">fast</t>
         </is>
@@ -3569,7 +3771,7 @@
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">i-intransitive</t>
         </is>
@@ -3585,7 +3787,7 @@
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">we-intransitive</t>
         </is>
@@ -3601,7 +3803,7 @@
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">you-intransitive</t>
         </is>
@@ -3617,7 +3819,7 @@
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">you-all-you-folks-intransitive</t>
         </is>
@@ -3633,7 +3835,7 @@
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">he-she-it-they-transitive-suffix</t>
         </is>
@@ -3649,7 +3851,7 @@
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">the-that-specific-article</t>
         </is>
@@ -3665,7 +3867,7 @@
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">your</t>
         </is>
@@ -3678,7 +3880,7 @@
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">work</t>
         </is>
@@ -3691,7 +3893,7 @@
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">salt</t>
         </is>
@@ -3704,7 +3906,7 @@
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">raven</t>
         </is>
@@ -3717,7 +3919,7 @@
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">grandparent</t>
         </is>
